--- a/public/xls/IN_OUT.xlsx
+++ b/public/xls/IN_OUT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b537af9f0bea1879/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{C8151176-CC2E-477D-8E84-2C1076901EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90AB397B-068E-4CCB-93A2-25A259DEF11C}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{C8151176-CC2E-477D-8E84-2C1076901EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E44B041-76C9-471C-9BAD-ACE2EB4E8649}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IN" sheetId="32" r:id="rId1"/>
@@ -165,7 +165,7 @@
     <numFmt numFmtId="165" formatCode="[$-FC22]d\ mmmm\ yyyy&quot; р.&quot;;@"/>
     <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy;@"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +277,13 @@
     </font>
     <font>
       <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -422,7 +429,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -462,7 +469,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -473,13 +479,6 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -488,55 +487,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -551,26 +508,68 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1159,68 +1158,68 @@
   <sheetData>
     <row r="1" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:10" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
@@ -1233,15 +1232,15 @@
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="54">
+      <c r="B9" s="32">
         <f ca="1">TODAY()</f>
         <v>46169</v>
       </c>
-      <c r="C9" s="54"/>
+      <c r="C9" s="32"/>
       <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1254,13 +1253,13 @@
       <c r="J10" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1273,329 +1272,329 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="49"/>
+      <c r="D16" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="26" t="s">
+      <c r="A17" s="33"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="31"/>
+      <c r="G17" s="33"/>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
+      <c r="A20" s="26"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
+      <c r="A35" s="26"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
+      <c r="A36" s="26"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
+      <c r="A37" s="26"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
+      <c r="A39" s="25"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
+      <c r="A41" s="25"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
+      <c r="A42" s="26"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
+      <c r="A45" s="26"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
+      <c r="A46" s="26"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
+      <c r="A48" s="26"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
     </row>
     <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="21"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="20"/>
       <c r="F49" s="10"/>
       <c r="G49" s="10"/>
     </row>
     <row r="50" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="21"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="20"/>
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
     </row>
@@ -1623,19 +1622,19 @@
     </row>
     <row r="56" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
-      <c r="E56" s="40" t="s">
+      <c r="E56" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="F56" s="40"/>
-      <c r="G56" s="55"/>
-    </row>
-    <row r="57" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F56" s="47"/>
+      <c r="G56" s="53"/>
+    </row>
+    <row r="57" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="28" t="s">
+      <c r="E57" s="23"/>
+      <c r="F57" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="56"/>
+      <c r="G57" s="54"/>
     </row>
     <row r="58" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
@@ -1657,7 +1656,7 @@
       <c r="F61" s="7"/>
     </row>
     <row r="62" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="25" t="s">
+      <c r="B62" s="21" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1671,29 +1670,29 @@
       <c r="G63" s="9"/>
     </row>
     <row r="64" spans="1:7" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="39" t="s">
+      <c r="A65" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="39"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="39"/>
-      <c r="F65" s="39"/>
-      <c r="G65" s="39"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="43"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
       <c r="E66" s="10"/>
       <c r="G66" s="1"/>
     </row>
@@ -1719,12 +1718,12 @@
       <c r="E70" s="10"/>
     </row>
     <row r="71" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="44"/>
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="44"/>
+      <c r="A71" s="41"/>
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
       <c r="G71" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1734,27 +1733,27 @@
       <c r="G72" s="7"/>
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="45"/>
-      <c r="B73" s="46"/>
-      <c r="C73" s="46"/>
-      <c r="D73" s="46"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="46"/>
-      <c r="G73" s="41"/>
+      <c r="A73" s="42"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="39"/>
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="45"/>
-      <c r="B74" s="46"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
+      <c r="A74" s="42"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="43"/>
       <c r="E74" s="12"/>
       <c r="F74" s="13"/>
-      <c r="G74" s="41"/>
+      <c r="G74" s="39"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="14"/>
-      <c r="B75" s="42"/>
-      <c r="C75" s="42"/>
+      <c r="B75" s="38"/>
+      <c r="C75" s="38"/>
       <c r="D75" s="15"/>
       <c r="E75" s="15"/>
       <c r="F75" s="14"/>
@@ -1762,8 +1761,8 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="14"/>
-      <c r="B76" s="42"/>
-      <c r="C76" s="42"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
       <c r="D76" s="15"/>
       <c r="E76" s="15"/>
       <c r="F76" s="14"/>
@@ -1771,8 +1770,8 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="14"/>
-      <c r="B77" s="42"/>
-      <c r="C77" s="42"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="38"/>
       <c r="D77" s="15"/>
       <c r="E77" s="15"/>
       <c r="F77" s="14"/>
@@ -1780,8 +1779,8 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="14"/>
-      <c r="B78" s="42"/>
-      <c r="C78" s="42"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
       <c r="D78" s="15"/>
       <c r="E78" s="15"/>
       <c r="F78" s="14"/>
@@ -1789,8 +1788,8 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="14"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="37"/>
       <c r="D79" s="15"/>
       <c r="E79" s="15"/>
       <c r="F79" s="14"/>
@@ -1798,8 +1797,8 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="14"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
       <c r="D80" s="15"/>
       <c r="E80" s="15"/>
       <c r="F80" s="14"/>
@@ -1807,8 +1806,8 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="14"/>
-      <c r="B81" s="47"/>
-      <c r="C81" s="47"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="37"/>
       <c r="D81" s="15"/>
       <c r="E81" s="15"/>
       <c r="F81" s="14"/>
@@ -1816,8 +1815,8 @@
     </row>
     <row r="82" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="14"/>
-      <c r="B82" s="47"/>
-      <c r="C82" s="47"/>
+      <c r="B82" s="37"/>
+      <c r="C82" s="37"/>
       <c r="D82" s="15"/>
       <c r="E82" s="15"/>
       <c r="F82" s="14"/>
@@ -1825,8 +1824,8 @@
     </row>
     <row r="83" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14"/>
-      <c r="B83" s="47"/>
-      <c r="C83" s="47"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="37"/>
       <c r="D83" s="15"/>
       <c r="E83" s="15"/>
       <c r="F83" s="14"/>
@@ -1834,8 +1833,8 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="14"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="47"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="37"/>
       <c r="D84" s="15"/>
       <c r="E84" s="15"/>
       <c r="F84" s="14"/>
@@ -1843,8 +1842,8 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="14"/>
-      <c r="B85" s="47"/>
-      <c r="C85" s="47"/>
+      <c r="B85" s="37"/>
+      <c r="C85" s="37"/>
       <c r="D85" s="15"/>
       <c r="E85" s="15"/>
       <c r="F85" s="14"/>
@@ -1852,8 +1851,8 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="14"/>
-      <c r="B86" s="47"/>
-      <c r="C86" s="47"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="37"/>
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
@@ -1861,8 +1860,8 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="14"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="47"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="37"/>
       <c r="D87" s="14"/>
       <c r="E87" s="14"/>
       <c r="F87" s="14"/>
@@ -1870,8 +1869,8 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="14"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="37"/>
       <c r="D88" s="14"/>
       <c r="E88" s="14"/>
       <c r="F88" s="14"/>
@@ -1879,8 +1878,8 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="14"/>
-      <c r="B89" s="47"/>
-      <c r="C89" s="47"/>
+      <c r="B89" s="37"/>
+      <c r="C89" s="37"/>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="14"/>
@@ -1888,8 +1887,8 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="14"/>
-      <c r="B90" s="47"/>
-      <c r="C90" s="47"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="37"/>
       <c r="D90" s="14"/>
       <c r="E90" s="14"/>
       <c r="F90" s="14"/>
@@ -1897,8 +1896,8 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="14"/>
-      <c r="B91" s="47"/>
-      <c r="C91" s="47"/>
+      <c r="B91" s="37"/>
+      <c r="C91" s="37"/>
       <c r="D91" s="14"/>
       <c r="E91" s="14"/>
       <c r="F91" s="14"/>
@@ -1906,8 +1905,8 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="14"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="47"/>
+      <c r="B92" s="37"/>
+      <c r="C92" s="37"/>
       <c r="D92" s="16"/>
       <c r="E92" s="14"/>
       <c r="F92" s="14"/>
@@ -1915,8 +1914,8 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="14"/>
-      <c r="B93" s="47"/>
-      <c r="C93" s="47"/>
+      <c r="B93" s="37"/>
+      <c r="C93" s="37"/>
       <c r="D93" s="16"/>
       <c r="E93" s="14"/>
       <c r="F93" s="14"/>
@@ -1924,8 +1923,8 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="14"/>
-      <c r="B94" s="47"/>
-      <c r="C94" s="47"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="37"/>
       <c r="D94" s="16"/>
       <c r="E94" s="14"/>
       <c r="F94" s="14"/>
@@ -1959,15 +1958,77 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:C74"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
@@ -1992,77 +2053,15 @@
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="F25:G25"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:C74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -2090,68 +2089,68 @@
   <sheetData>
     <row r="1" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:10" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
@@ -2164,15 +2163,15 @@
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="54">
+      <c r="B9" s="32">
         <f ca="1">TODAY()</f>
         <v>46169</v>
       </c>
-      <c r="C9" s="54"/>
+      <c r="C9" s="32"/>
       <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
@@ -2185,13 +2184,13 @@
       <c r="J10" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -2204,329 +2203,329 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="49"/>
+      <c r="D16" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="26" t="s">
+      <c r="A17" s="33"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="31"/>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
+      <c r="G17" s="33"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="26"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
+      <c r="A20" s="26"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="26"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="53"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
+      <c r="A35" s="26"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
+      <c r="A36" s="26"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
+      <c r="A37" s="26"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
+      <c r="A39" s="25"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
+      <c r="A41" s="25"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
+      <c r="A42" s="26"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-    </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-    </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-    </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="26"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="26"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="26"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="26"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
     </row>
     <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="21"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="20"/>
       <c r="F49" s="10"/>
       <c r="G49" s="10"/>
     </row>
     <row r="50" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="21"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="20"/>
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
     </row>
@@ -2554,19 +2553,19 @@
     </row>
     <row r="56" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
-      <c r="E56" s="40" t="s">
+      <c r="E56" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="F56" s="40"/>
-      <c r="G56" s="55"/>
-    </row>
-    <row r="57" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F56" s="47"/>
+      <c r="G56" s="53"/>
+    </row>
+    <row r="57" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="28" t="s">
+      <c r="E57" s="23"/>
+      <c r="F57" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="56"/>
+      <c r="G57" s="54"/>
     </row>
     <row r="58" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
@@ -2588,7 +2587,7 @@
       <c r="F61" s="7"/>
     </row>
     <row r="62" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="25" t="s">
+      <c r="B62" s="21" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2602,29 +2601,29 @@
       <c r="G63" s="9"/>
     </row>
     <row r="64" spans="1:7" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="39" t="s">
+      <c r="A65" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="39"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="39"/>
-      <c r="F65" s="39"/>
-      <c r="G65" s="39"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="43"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
       <c r="E66" s="10"/>
       <c r="G66" s="1"/>
     </row>
@@ -2650,12 +2649,12 @@
       <c r="E70" s="10"/>
     </row>
     <row r="71" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="44"/>
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="44"/>
+      <c r="A71" s="41"/>
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
       <c r="G71" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2665,27 +2664,27 @@
       <c r="G72" s="7"/>
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="45"/>
-      <c r="B73" s="46"/>
-      <c r="C73" s="46"/>
-      <c r="D73" s="46"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="46"/>
-      <c r="G73" s="41"/>
+      <c r="A73" s="42"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="39"/>
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="45"/>
-      <c r="B74" s="46"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
+      <c r="A74" s="42"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="43"/>
       <c r="E74" s="12"/>
       <c r="F74" s="13"/>
-      <c r="G74" s="41"/>
+      <c r="G74" s="39"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="14"/>
-      <c r="B75" s="42"/>
-      <c r="C75" s="42"/>
+      <c r="B75" s="38"/>
+      <c r="C75" s="38"/>
       <c r="D75" s="15"/>
       <c r="E75" s="15"/>
       <c r="F75" s="14"/>
@@ -2693,8 +2692,8 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="14"/>
-      <c r="B76" s="42"/>
-      <c r="C76" s="42"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
       <c r="D76" s="15"/>
       <c r="E76" s="15"/>
       <c r="F76" s="14"/>
@@ -2702,8 +2701,8 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="14"/>
-      <c r="B77" s="42"/>
-      <c r="C77" s="42"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="38"/>
       <c r="D77" s="15"/>
       <c r="E77" s="15"/>
       <c r="F77" s="14"/>
@@ -2711,8 +2710,8 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="14"/>
-      <c r="B78" s="42"/>
-      <c r="C78" s="42"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
       <c r="D78" s="15"/>
       <c r="E78" s="15"/>
       <c r="F78" s="14"/>
@@ -2720,8 +2719,8 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="14"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="37"/>
       <c r="D79" s="15"/>
       <c r="E79" s="15"/>
       <c r="F79" s="14"/>
@@ -2729,8 +2728,8 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="14"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
       <c r="D80" s="15"/>
       <c r="E80" s="15"/>
       <c r="F80" s="14"/>
@@ -2738,8 +2737,8 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="14"/>
-      <c r="B81" s="47"/>
-      <c r="C81" s="47"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="37"/>
       <c r="D81" s="15"/>
       <c r="E81" s="15"/>
       <c r="F81" s="14"/>
@@ -2747,8 +2746,8 @@
     </row>
     <row r="82" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="14"/>
-      <c r="B82" s="47"/>
-      <c r="C82" s="47"/>
+      <c r="B82" s="37"/>
+      <c r="C82" s="37"/>
       <c r="D82" s="15"/>
       <c r="E82" s="15"/>
       <c r="F82" s="14"/>
@@ -2756,8 +2755,8 @@
     </row>
     <row r="83" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14"/>
-      <c r="B83" s="47"/>
-      <c r="C83" s="47"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="37"/>
       <c r="D83" s="15"/>
       <c r="E83" s="15"/>
       <c r="F83" s="14"/>
@@ -2765,8 +2764,8 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="14"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="47"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="37"/>
       <c r="D84" s="15"/>
       <c r="E84" s="15"/>
       <c r="F84" s="14"/>
@@ -2774,8 +2773,8 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="14"/>
-      <c r="B85" s="47"/>
-      <c r="C85" s="47"/>
+      <c r="B85" s="37"/>
+      <c r="C85" s="37"/>
       <c r="D85" s="15"/>
       <c r="E85" s="15"/>
       <c r="F85" s="14"/>
@@ -2783,8 +2782,8 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="14"/>
-      <c r="B86" s="47"/>
-      <c r="C86" s="47"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="37"/>
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
@@ -2792,8 +2791,8 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="14"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="47"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="37"/>
       <c r="D87" s="14"/>
       <c r="E87" s="14"/>
       <c r="F87" s="14"/>
@@ -2801,8 +2800,8 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="14"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="37"/>
       <c r="D88" s="14"/>
       <c r="E88" s="14"/>
       <c r="F88" s="14"/>
@@ -2810,8 +2809,8 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="14"/>
-      <c r="B89" s="47"/>
-      <c r="C89" s="47"/>
+      <c r="B89" s="37"/>
+      <c r="C89" s="37"/>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="14"/>
@@ -2819,8 +2818,8 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="14"/>
-      <c r="B90" s="47"/>
-      <c r="C90" s="47"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="37"/>
       <c r="D90" s="14"/>
       <c r="E90" s="14"/>
       <c r="F90" s="14"/>
@@ -2828,8 +2827,8 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="14"/>
-      <c r="B91" s="47"/>
-      <c r="C91" s="47"/>
+      <c r="B91" s="37"/>
+      <c r="C91" s="37"/>
       <c r="D91" s="14"/>
       <c r="E91" s="14"/>
       <c r="F91" s="14"/>
@@ -2837,8 +2836,8 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="14"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="47"/>
+      <c r="B92" s="37"/>
+      <c r="C92" s="37"/>
       <c r="D92" s="16"/>
       <c r="E92" s="14"/>
       <c r="F92" s="14"/>
@@ -2846,8 +2845,8 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="14"/>
-      <c r="B93" s="47"/>
-      <c r="C93" s="47"/>
+      <c r="B93" s="37"/>
+      <c r="C93" s="37"/>
       <c r="D93" s="16"/>
       <c r="E93" s="14"/>
       <c r="F93" s="14"/>
@@ -2855,8 +2854,8 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="14"/>
-      <c r="B94" s="47"/>
-      <c r="C94" s="47"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="37"/>
       <c r="D94" s="16"/>
       <c r="E94" s="14"/>
       <c r="F94" s="14"/>
@@ -2890,6 +2889,94 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
@@ -2906,94 +2993,6 @@
     <mergeCell ref="D73:D74"/>
     <mergeCell ref="E73:F73"/>
     <mergeCell ref="G73:G74"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="F19:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -3025,120 +3024,120 @@
   <sheetData>
     <row r="1" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:14" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
     </row>
     <row r="3" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
     </row>
     <row r="4" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
     </row>
     <row r="6" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
     </row>
     <row r="7" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
     </row>
     <row r="8" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
@@ -3158,26 +3157,26 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="54">
+      <c r="B9" s="32">
         <f ca="1">TODAY()</f>
         <v>46169</v>
       </c>
-      <c r="C9" s="54"/>
+      <c r="C9" s="32"/>
       <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="54">
+      <c r="I9" s="32">
         <f ca="1">TODAY()</f>
         <v>46169</v>
       </c>
-      <c r="J9" s="54"/>
+      <c r="J9" s="32"/>
       <c r="N9" s="2" t="s">
         <v>12</v>
       </c>
@@ -3191,20 +3190,20 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -3223,1051 +3222,1051 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="49"/>
+      <c r="D16" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31" t="s">
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="I16" s="33" t="s">
+      <c r="I16" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="J16" s="33"/>
-      <c r="K16" s="31" t="s">
+      <c r="J16" s="49"/>
+      <c r="K16" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="31" t="s">
+      <c r="L16" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="26" t="s">
+      <c r="A17" s="33"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="26" t="s">
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="M17" s="31" t="s">
+      <c r="M17" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="N17" s="31"/>
+      <c r="N17" s="33"/>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="17" t="str">
+      <c r="A18" s="26"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="26" t="str">
         <f>IF(A18&lt;&gt;"",A18,"")</f>
         <v/>
       </c>
-      <c r="I18" s="34" t="str">
+      <c r="I18" s="35" t="str">
         <f>IF(B18&lt;&gt;"",B18,"")</f>
         <v/>
       </c>
-      <c r="J18" s="35"/>
-      <c r="K18" s="17" t="str">
+      <c r="J18" s="36"/>
+      <c r="K18" s="26" t="str">
         <f>IF(D18&lt;&gt;"",D18,"")</f>
         <v/>
       </c>
-      <c r="L18" s="17" t="str">
+      <c r="L18" s="26" t="str">
         <f>IF(E18&lt;&gt;"",E18,"")</f>
         <v/>
       </c>
-      <c r="M18" s="57" t="str">
+      <c r="M18" s="51" t="str">
         <f>IF(F18&lt;&gt;"",F18,"")</f>
         <v/>
       </c>
-      <c r="N18" s="58"/>
+      <c r="N18" s="52"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="17" t="str">
+      <c r="A19" s="26"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="26" t="str">
         <f t="shared" ref="H19:H48" si="0">IF(A19&lt;&gt;"",A19,"")</f>
         <v/>
       </c>
-      <c r="I19" s="34" t="str">
+      <c r="I19" s="35" t="str">
         <f t="shared" ref="I19:I48" si="1">IF(B19&lt;&gt;"",B19,"")</f>
         <v/>
       </c>
-      <c r="J19" s="35"/>
-      <c r="K19" s="17" t="str">
+      <c r="J19" s="36"/>
+      <c r="K19" s="26" t="str">
         <f t="shared" ref="K19:K48" si="2">IF(D19&lt;&gt;"",D19,"")</f>
         <v/>
       </c>
-      <c r="L19" s="17" t="str">
+      <c r="L19" s="26" t="str">
         <f t="shared" ref="L19:L48" si="3">IF(E19&lt;&gt;"",E19,"")</f>
         <v/>
       </c>
-      <c r="M19" s="57" t="str">
+      <c r="M19" s="51" t="str">
         <f t="shared" ref="M19:M48" si="4">IF(F19&lt;&gt;"",F19,"")</f>
         <v/>
       </c>
-      <c r="N19" s="58"/>
+      <c r="N19" s="52"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="17" t="str">
+      <c r="A20" s="26"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I20" s="34" t="str">
+      <c r="I20" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J20" s="35"/>
-      <c r="K20" s="17" t="str">
+      <c r="J20" s="36"/>
+      <c r="K20" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L20" s="17" t="str">
+      <c r="L20" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M20" s="57" t="str">
+      <c r="M20" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N20" s="58"/>
+      <c r="N20" s="52"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="17" t="str">
+      <c r="A21" s="26"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I21" s="34" t="str">
+      <c r="I21" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J21" s="35"/>
-      <c r="K21" s="17" t="str">
+      <c r="J21" s="36"/>
+      <c r="K21" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L21" s="17" t="str">
+      <c r="L21" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M21" s="57" t="str">
+      <c r="M21" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N21" s="58"/>
+      <c r="N21" s="52"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="17" t="str">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I22" s="34" t="str">
+      <c r="I22" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J22" s="35"/>
-      <c r="K22" s="17" t="str">
+      <c r="J22" s="36"/>
+      <c r="K22" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L22" s="17" t="str">
+      <c r="L22" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M22" s="57" t="str">
+      <c r="M22" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N22" s="58"/>
+      <c r="N22" s="52"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="17" t="str">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I23" s="34" t="str">
+      <c r="I23" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J23" s="35"/>
-      <c r="K23" s="17" t="str">
+      <c r="J23" s="36"/>
+      <c r="K23" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L23" s="17" t="str">
+      <c r="L23" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M23" s="57" t="str">
+      <c r="M23" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N23" s="58"/>
+      <c r="N23" s="52"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="17" t="str">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I24" s="34" t="str">
+      <c r="I24" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J24" s="35"/>
-      <c r="K24" s="17" t="str">
+      <c r="J24" s="36"/>
+      <c r="K24" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L24" s="17" t="str">
+      <c r="L24" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M24" s="57" t="str">
+      <c r="M24" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N24" s="58"/>
+      <c r="N24" s="52"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="17" t="str">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I25" s="34" t="str">
+      <c r="I25" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J25" s="35"/>
-      <c r="K25" s="17" t="str">
+      <c r="J25" s="36"/>
+      <c r="K25" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L25" s="17" t="str">
+      <c r="L25" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M25" s="57" t="str">
+      <c r="M25" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N25" s="58"/>
+      <c r="N25" s="52"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="17" t="str">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I26" s="34" t="str">
+      <c r="I26" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J26" s="35"/>
-      <c r="K26" s="17" t="str">
+      <c r="J26" s="36"/>
+      <c r="K26" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L26" s="17" t="str">
+      <c r="L26" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M26" s="57" t="str">
+      <c r="M26" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N26" s="58"/>
+      <c r="N26" s="52"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="17" t="str">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I27" s="34" t="str">
+      <c r="I27" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J27" s="35"/>
-      <c r="K27" s="17" t="str">
+      <c r="J27" s="36"/>
+      <c r="K27" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L27" s="17" t="str">
+      <c r="L27" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M27" s="57" t="str">
+      <c r="M27" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N27" s="58"/>
+      <c r="N27" s="52"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="17" t="str">
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I28" s="34" t="str">
+      <c r="I28" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J28" s="35"/>
-      <c r="K28" s="17" t="str">
+      <c r="J28" s="36"/>
+      <c r="K28" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L28" s="17" t="str">
+      <c r="L28" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M28" s="57" t="str">
+      <c r="M28" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N28" s="58"/>
+      <c r="N28" s="52"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="17" t="str">
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I29" s="34" t="str">
+      <c r="I29" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J29" s="35"/>
-      <c r="K29" s="17" t="str">
+      <c r="J29" s="36"/>
+      <c r="K29" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L29" s="17" t="str">
+      <c r="L29" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M29" s="57" t="str">
+      <c r="M29" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N29" s="58"/>
+      <c r="N29" s="52"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="17" t="str">
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I30" s="34" t="str">
+      <c r="I30" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J30" s="35"/>
-      <c r="K30" s="17" t="str">
+      <c r="J30" s="36"/>
+      <c r="K30" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L30" s="17" t="str">
+      <c r="L30" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M30" s="57" t="str">
+      <c r="M30" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N30" s="58"/>
+      <c r="N30" s="52"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="17" t="str">
+      <c r="A31" s="26"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I31" s="34" t="str">
+      <c r="I31" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J31" s="35"/>
-      <c r="K31" s="17" t="str">
+      <c r="J31" s="36"/>
+      <c r="K31" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L31" s="17" t="str">
+      <c r="L31" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M31" s="57" t="str">
+      <c r="M31" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N31" s="58"/>
+      <c r="N31" s="52"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="17" t="str">
+      <c r="A32" s="26"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I32" s="34" t="str">
+      <c r="I32" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J32" s="35"/>
-      <c r="K32" s="17" t="str">
+      <c r="J32" s="36"/>
+      <c r="K32" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L32" s="17" t="str">
+      <c r="L32" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M32" s="57" t="str">
+      <c r="M32" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N32" s="58"/>
+      <c r="N32" s="52"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="17" t="str">
+      <c r="A33" s="26"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I33" s="34" t="str">
+      <c r="I33" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J33" s="35"/>
-      <c r="K33" s="17" t="str">
+      <c r="J33" s="36"/>
+      <c r="K33" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L33" s="17" t="str">
+      <c r="L33" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M33" s="57" t="str">
+      <c r="M33" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N33" s="58"/>
+      <c r="N33" s="52"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="17" t="str">
+      <c r="A34" s="26"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I34" s="34" t="str">
+      <c r="I34" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J34" s="35"/>
-      <c r="K34" s="17" t="str">
+      <c r="J34" s="36"/>
+      <c r="K34" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L34" s="17" t="str">
+      <c r="L34" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M34" s="57" t="str">
+      <c r="M34" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N34" s="58"/>
+      <c r="N34" s="52"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="17" t="str">
+      <c r="A35" s="26"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I35" s="34" t="str">
+      <c r="I35" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J35" s="35"/>
-      <c r="K35" s="17" t="str">
+      <c r="J35" s="36"/>
+      <c r="K35" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L35" s="17" t="str">
+      <c r="L35" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M35" s="57" t="str">
+      <c r="M35" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N35" s="58"/>
+      <c r="N35" s="52"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="17" t="str">
+      <c r="A36" s="26"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I36" s="34" t="str">
+      <c r="I36" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J36" s="35"/>
-      <c r="K36" s="17" t="str">
+      <c r="J36" s="36"/>
+      <c r="K36" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L36" s="17" t="str">
+      <c r="L36" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M36" s="57" t="str">
+      <c r="M36" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N36" s="58"/>
+      <c r="N36" s="52"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="17" t="str">
+      <c r="A37" s="26"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I37" s="34" t="str">
+      <c r="I37" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J37" s="35"/>
-      <c r="K37" s="17" t="str">
+      <c r="J37" s="36"/>
+      <c r="K37" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L37" s="17" t="str">
+      <c r="L37" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M37" s="57" t="str">
+      <c r="M37" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N37" s="58"/>
+      <c r="N37" s="52"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="17" t="str">
+      <c r="A38" s="26"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I38" s="34" t="str">
+      <c r="I38" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J38" s="35"/>
-      <c r="K38" s="17" t="str">
+      <c r="J38" s="36"/>
+      <c r="K38" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L38" s="17" t="str">
+      <c r="L38" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M38" s="57" t="str">
+      <c r="M38" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N38" s="58"/>
+      <c r="N38" s="52"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="17" t="str">
+      <c r="A39" s="25"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I39" s="34" t="str">
+      <c r="I39" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J39" s="35"/>
-      <c r="K39" s="17" t="str">
+      <c r="J39" s="36"/>
+      <c r="K39" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L39" s="17" t="str">
+      <c r="L39" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M39" s="57" t="str">
+      <c r="M39" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N39" s="58"/>
+      <c r="N39" s="52"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="17" t="str">
+      <c r="A40" s="26"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I40" s="34" t="str">
+      <c r="I40" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J40" s="35"/>
-      <c r="K40" s="17" t="str">
+      <c r="J40" s="36"/>
+      <c r="K40" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L40" s="17" t="str">
+      <c r="L40" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M40" s="57" t="str">
+      <c r="M40" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N40" s="58"/>
+      <c r="N40" s="52"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="17" t="str">
+      <c r="A41" s="25"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I41" s="34" t="str">
+      <c r="I41" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J41" s="35"/>
-      <c r="K41" s="17" t="str">
+      <c r="J41" s="36"/>
+      <c r="K41" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L41" s="17" t="str">
+      <c r="L41" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M41" s="57" t="str">
+      <c r="M41" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N41" s="58"/>
+      <c r="N41" s="52"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="17" t="str">
+      <c r="A42" s="26"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I42" s="34" t="str">
+      <c r="I42" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J42" s="35"/>
-      <c r="K42" s="17" t="str">
+      <c r="J42" s="36"/>
+      <c r="K42" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L42" s="17" t="str">
+      <c r="L42" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M42" s="57" t="str">
+      <c r="M42" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N42" s="58"/>
+      <c r="N42" s="52"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="17" t="str">
+      <c r="A43" s="26"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I43" s="34" t="str">
+      <c r="I43" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J43" s="35"/>
-      <c r="K43" s="17" t="str">
+      <c r="J43" s="36"/>
+      <c r="K43" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L43" s="17" t="str">
+      <c r="L43" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M43" s="57" t="str">
+      <c r="M43" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N43" s="58"/>
+      <c r="N43" s="52"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="17" t="str">
+      <c r="A44" s="26"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I44" s="34" t="str">
+      <c r="I44" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J44" s="35"/>
-      <c r="K44" s="17" t="str">
+      <c r="J44" s="36"/>
+      <c r="K44" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L44" s="17" t="str">
+      <c r="L44" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M44" s="57" t="str">
+      <c r="M44" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N44" s="58"/>
+      <c r="N44" s="52"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="17" t="str">
+      <c r="A45" s="26"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I45" s="34" t="str">
+      <c r="I45" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J45" s="35"/>
-      <c r="K45" s="17" t="str">
+      <c r="J45" s="36"/>
+      <c r="K45" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L45" s="17" t="str">
+      <c r="L45" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M45" s="57" t="str">
+      <c r="M45" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N45" s="58"/>
+      <c r="N45" s="52"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="17" t="str">
+      <c r="A46" s="26"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I46" s="34" t="str">
+      <c r="I46" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J46" s="35"/>
-      <c r="K46" s="17" t="str">
+      <c r="J46" s="36"/>
+      <c r="K46" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L46" s="17" t="str">
+      <c r="L46" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M46" s="57" t="str">
+      <c r="M46" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N46" s="58"/>
+      <c r="N46" s="52"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="17" t="str">
+      <c r="A47" s="26"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="51"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I47" s="34" t="str">
+      <c r="I47" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J47" s="35"/>
-      <c r="K47" s="17" t="str">
+      <c r="J47" s="36"/>
+      <c r="K47" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L47" s="17" t="str">
+      <c r="L47" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M47" s="57" t="str">
+      <c r="M47" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N47" s="58"/>
+      <c r="N47" s="52"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="17" t="str">
+      <c r="A48" s="26"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="51"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I48" s="34" t="str">
+      <c r="I48" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J48" s="35"/>
-      <c r="K48" s="17" t="str">
+      <c r="J48" s="36"/>
+      <c r="K48" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L48" s="17" t="str">
+      <c r="L48" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M48" s="57" t="str">
+      <c r="M48" s="51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N48" s="58"/>
+      <c r="N48" s="52"/>
     </row>
     <row r="49" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="21"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="20"/>
       <c r="F49" s="10"/>
       <c r="G49" s="10"/>
       <c r="H49" s="13"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="20"/>
-      <c r="L49" s="21"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="20"/>
       <c r="M49" s="10"/>
       <c r="N49" s="10"/>
     </row>
     <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="21"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="20"/>
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
       <c r="H50" s="13"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="20"/>
-      <c r="L50" s="21"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="20"/>
       <c r="M50" s="10"/>
       <c r="N50" s="10"/>
     </row>
@@ -4308,31 +4307,37 @@
     </row>
     <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
-      <c r="E56" s="40" t="s">
+      <c r="E56" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="F56" s="40"/>
-      <c r="G56" s="55"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="53"/>
       <c r="H56" s="3"/>
-      <c r="L56" s="40" t="s">
+      <c r="L56" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="M56" s="40"/>
-      <c r="N56" s="55"/>
-    </row>
-    <row r="57" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M56" s="47"/>
+      <c r="N56" s="53" t="str">
+        <f>IF(G56&lt;&gt;"",G56,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="28" t="s">
+      <c r="E57" s="23"/>
+      <c r="F57" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="56"/>
+      <c r="G57" s="54"/>
       <c r="H57" s="3"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="28" t="s">
+      <c r="L57" s="23"/>
+      <c r="M57" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="N57" s="56"/>
+      <c r="N57" s="54" t="str">
+        <f>IF(G57&lt;&gt;"",G57,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="58" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
@@ -4365,10 +4370,10 @@
       <c r="M61" s="7"/>
     </row>
     <row r="62" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="25" t="s">
+      <c r="B62" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="I62" s="25" t="s">
+      <c r="I62" s="21" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4389,45 +4394,45 @@
       <c r="N63" s="9"/>
     </row>
     <row r="64" spans="1:14" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="18"/>
-      <c r="I64" s="18"/>
-      <c r="J64" s="18"/>
-      <c r="K64" s="18"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="17"/>
+      <c r="K64" s="17"/>
+      <c r="L64" s="17"/>
+      <c r="M64" s="17"/>
+      <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="39" t="s">
+      <c r="A65" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="39"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="39"/>
-      <c r="F65" s="39"/>
-      <c r="G65" s="39"/>
-      <c r="H65" s="39" t="s">
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="I65" s="39"/>
-      <c r="J65" s="39"/>
-      <c r="K65" s="39"/>
-      <c r="L65" s="39"/>
-      <c r="M65" s="39"/>
-      <c r="N65" s="39"/>
+      <c r="I65" s="44"/>
+      <c r="J65" s="44"/>
+      <c r="K65" s="44"/>
+      <c r="L65" s="44"/>
+      <c r="M65" s="44"/>
+      <c r="N65" s="44"/>
     </row>
     <row r="66" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="43"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
       <c r="E66" s="10"/>
       <c r="G66" s="1"/>
     </row>
@@ -4453,12 +4458,12 @@
       <c r="E70" s="10"/>
     </row>
     <row r="71" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="44"/>
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="44"/>
+      <c r="A71" s="41"/>
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
       <c r="G71" s="11"/>
     </row>
     <row r="72" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4468,27 +4473,27 @@
       <c r="G72" s="7"/>
     </row>
     <row r="73" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="45"/>
-      <c r="B73" s="46"/>
-      <c r="C73" s="46"/>
-      <c r="D73" s="46"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="46"/>
-      <c r="G73" s="41"/>
+      <c r="A73" s="42"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="39"/>
     </row>
     <row r="74" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="45"/>
-      <c r="B74" s="46"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
+      <c r="A74" s="42"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="43"/>
       <c r="E74" s="12"/>
       <c r="F74" s="13"/>
-      <c r="G74" s="41"/>
+      <c r="G74" s="39"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="14"/>
-      <c r="B75" s="42"/>
-      <c r="C75" s="42"/>
+      <c r="B75" s="38"/>
+      <c r="C75" s="38"/>
       <c r="D75" s="15"/>
       <c r="E75" s="15"/>
       <c r="F75" s="14"/>
@@ -4496,8 +4501,8 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="14"/>
-      <c r="B76" s="42"/>
-      <c r="C76" s="42"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
       <c r="D76" s="15"/>
       <c r="E76" s="15"/>
       <c r="F76" s="14"/>
@@ -4505,8 +4510,8 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="14"/>
-      <c r="B77" s="42"/>
-      <c r="C77" s="42"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="38"/>
       <c r="D77" s="15"/>
       <c r="E77" s="15"/>
       <c r="F77" s="14"/>
@@ -4514,8 +4519,8 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="14"/>
-      <c r="B78" s="42"/>
-      <c r="C78" s="42"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
       <c r="D78" s="15"/>
       <c r="E78" s="15"/>
       <c r="F78" s="14"/>
@@ -4523,8 +4528,8 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="14"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="37"/>
       <c r="D79" s="15"/>
       <c r="E79" s="15"/>
       <c r="F79" s="14"/>
@@ -4532,8 +4537,8 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="14"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
       <c r="D80" s="15"/>
       <c r="E80" s="15"/>
       <c r="F80" s="14"/>
@@ -4541,8 +4546,8 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="14"/>
-      <c r="B81" s="47"/>
-      <c r="C81" s="47"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="37"/>
       <c r="D81" s="15"/>
       <c r="E81" s="15"/>
       <c r="F81" s="14"/>
@@ -4550,8 +4555,8 @@
     </row>
     <row r="82" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="14"/>
-      <c r="B82" s="47"/>
-      <c r="C82" s="47"/>
+      <c r="B82" s="37"/>
+      <c r="C82" s="37"/>
       <c r="D82" s="15"/>
       <c r="E82" s="15"/>
       <c r="F82" s="14"/>
@@ -4559,8 +4564,8 @@
     </row>
     <row r="83" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14"/>
-      <c r="B83" s="47"/>
-      <c r="C83" s="47"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="37"/>
       <c r="D83" s="15"/>
       <c r="E83" s="15"/>
       <c r="F83" s="14"/>
@@ -4568,8 +4573,8 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="14"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="47"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="37"/>
       <c r="D84" s="15"/>
       <c r="E84" s="15"/>
       <c r="F84" s="14"/>
@@ -4577,8 +4582,8 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="14"/>
-      <c r="B85" s="47"/>
-      <c r="C85" s="47"/>
+      <c r="B85" s="37"/>
+      <c r="C85" s="37"/>
       <c r="D85" s="15"/>
       <c r="E85" s="15"/>
       <c r="F85" s="14"/>
@@ -4586,8 +4591,8 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="14"/>
-      <c r="B86" s="47"/>
-      <c r="C86" s="47"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="37"/>
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
@@ -4595,8 +4600,8 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="14"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="47"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="37"/>
       <c r="D87" s="14"/>
       <c r="E87" s="14"/>
       <c r="F87" s="14"/>
@@ -4604,8 +4609,8 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="14"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="37"/>
       <c r="D88" s="14"/>
       <c r="E88" s="14"/>
       <c r="F88" s="14"/>
@@ -4613,8 +4618,8 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="14"/>
-      <c r="B89" s="47"/>
-      <c r="C89" s="47"/>
+      <c r="B89" s="37"/>
+      <c r="C89" s="37"/>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="14"/>
@@ -4622,8 +4627,8 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="14"/>
-      <c r="B90" s="47"/>
-      <c r="C90" s="47"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="37"/>
       <c r="D90" s="14"/>
       <c r="E90" s="14"/>
       <c r="F90" s="14"/>
@@ -4631,8 +4636,8 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="14"/>
-      <c r="B91" s="47"/>
-      <c r="C91" s="47"/>
+      <c r="B91" s="37"/>
+      <c r="C91" s="37"/>
       <c r="D91" s="14"/>
       <c r="E91" s="14"/>
       <c r="F91" s="14"/>
@@ -4640,8 +4645,8 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="14"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="47"/>
+      <c r="B92" s="37"/>
+      <c r="C92" s="37"/>
       <c r="D92" s="16"/>
       <c r="E92" s="14"/>
       <c r="F92" s="14"/>
@@ -4649,8 +4654,8 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="14"/>
-      <c r="B93" s="47"/>
-      <c r="C93" s="47"/>
+      <c r="B93" s="37"/>
+      <c r="C93" s="37"/>
       <c r="D93" s="16"/>
       <c r="E93" s="14"/>
       <c r="F93" s="14"/>
@@ -4658,8 +4663,8 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="14"/>
-      <c r="B94" s="47"/>
-      <c r="C94" s="47"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="37"/>
       <c r="D94" s="16"/>
       <c r="E94" s="14"/>
       <c r="F94" s="14"/>
@@ -4693,68 +4698,101 @@
     </row>
   </sheetData>
   <mergeCells count="181">
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="H65:N65"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:C74"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
     <mergeCell ref="I16:J17"/>
     <mergeCell ref="K16:K17"/>
     <mergeCell ref="L16:N16"/>
@@ -4779,101 +4817,68 @@
     <mergeCell ref="B93:C93"/>
     <mergeCell ref="B82:C82"/>
     <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:C74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="H65:N65"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="M45:N45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="portrait" r:id="rId1"/>
